--- a/artfynd/A 51531-2024 artfynd.xlsx
+++ b/artfynd/A 51531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121500809</v>
+        <v>121501806</v>
       </c>
       <c r="B2" t="n">
-        <v>94588</v>
+        <v>79592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562703</v>
+        <v>562590</v>
       </c>
       <c r="R2" t="n">
-        <v>6515245</v>
+        <v>6515240</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Finspång</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Skedevi</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501806</v>
+        <v>121500341</v>
       </c>
       <c r="B3" t="n">
-        <v>79592</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562590</v>
+        <v>562649</v>
       </c>
       <c r="R3" t="n">
-        <v>6515240</v>
+        <v>6515253</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Finspång</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Skedevi</t>
+          <t>Simonstorp</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>121500360</v>
       </c>
       <c r="B4" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121500789</v>
+        <v>121500809</v>
       </c>
       <c r="B5" t="n">
-        <v>79723</v>
+        <v>94588</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562707</v>
+        <v>562703</v>
       </c>
       <c r="R5" t="n">
-        <v>6515242</v>
+        <v>6515245</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500341</v>
+        <v>121500789</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>79723</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562649</v>
+        <v>562707</v>
       </c>
       <c r="R6" t="n">
-        <v>6515253</v>
+        <v>6515242</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>

--- a/artfynd/A 51531-2024 artfynd.xlsx
+++ b/artfynd/A 51531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121501806</v>
+        <v>121500360</v>
       </c>
       <c r="B2" t="n">
-        <v>79592</v>
+        <v>100364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562590</v>
+        <v>562643</v>
       </c>
       <c r="R2" t="n">
-        <v>6515240</v>
+        <v>6515265</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Finspång</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Skedevi</t>
+          <t>Simonstorp</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121500341</v>
+        <v>121501806</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>79592</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562649</v>
+        <v>562590</v>
       </c>
       <c r="R3" t="n">
-        <v>6515253</v>
+        <v>6515240</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Finspång</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Skedevi</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121500360</v>
+        <v>121500789</v>
       </c>
       <c r="B4" t="n">
-        <v>100364</v>
+        <v>79723</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562643</v>
+        <v>562707</v>
       </c>
       <c r="R4" t="n">
-        <v>6515265</v>
+        <v>6515242</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500789</v>
+        <v>121500825</v>
       </c>
       <c r="B6" t="n">
-        <v>79723</v>
+        <v>88501</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>805</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Scharlakansvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562707</v>
+        <v>562686</v>
       </c>
       <c r="R6" t="n">
-        <v>6515242</v>
+        <v>6515292</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1177,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500825</v>
+        <v>121500341</v>
       </c>
       <c r="B7" t="n">
-        <v>88501</v>
+        <v>79688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,41 +1205,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>805</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562686</v>
+        <v>562649</v>
       </c>
       <c r="R7" t="n">
-        <v>6515292</v>
+        <v>6515253</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 51531-2024 artfynd.xlsx
+++ b/artfynd/A 51531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121500360</v>
+        <v>121500809</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
+        <v>94594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562643</v>
+        <v>562703</v>
       </c>
       <c r="R2" t="n">
-        <v>6515265</v>
+        <v>6515245</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501806</v>
+        <v>121500360</v>
       </c>
       <c r="B3" t="n">
-        <v>79592</v>
+        <v>100370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562590</v>
+        <v>562643</v>
       </c>
       <c r="R3" t="n">
-        <v>6515240</v>
+        <v>6515265</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Finspång</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Skedevi</t>
+          <t>Simonstorp</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121500789</v>
+        <v>121501806</v>
       </c>
       <c r="B4" t="n">
-        <v>79723</v>
+        <v>79593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562707</v>
+        <v>562590</v>
       </c>
       <c r="R4" t="n">
-        <v>6515242</v>
+        <v>6515240</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Finspång</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Skedevi</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121500809</v>
+        <v>121500789</v>
       </c>
       <c r="B5" t="n">
-        <v>94588</v>
+        <v>79724</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562703</v>
+        <v>562707</v>
       </c>
       <c r="R5" t="n">
-        <v>6515245</v>
+        <v>6515242</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500825</v>
+        <v>121500341</v>
       </c>
       <c r="B6" t="n">
-        <v>88501</v>
+        <v>79689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,41 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>805</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562686</v>
+        <v>562649</v>
       </c>
       <c r="R6" t="n">
-        <v>6515292</v>
+        <v>6515253</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500341</v>
+        <v>121500825</v>
       </c>
       <c r="B7" t="n">
-        <v>79688</v>
+        <v>88505</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,37 +1201,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>805</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Scharlakansvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562649</v>
+        <v>562686</v>
       </c>
       <c r="R7" t="n">
-        <v>6515253</v>
+        <v>6515292</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 51531-2024 artfynd.xlsx
+++ b/artfynd/A 51531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121500809</v>
+        <v>121501806</v>
       </c>
       <c r="B2" t="n">
-        <v>94594</v>
+        <v>79594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562703</v>
+        <v>562590</v>
       </c>
       <c r="R2" t="n">
-        <v>6515245</v>
+        <v>6515240</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Finspång</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Skedevi</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -765,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +780,7 @@
         <v>121500360</v>
       </c>
       <c r="B3" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121501806</v>
+        <v>121500809</v>
       </c>
       <c r="B4" t="n">
-        <v>79593</v>
+        <v>94595</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562590</v>
+        <v>562703</v>
       </c>
       <c r="R4" t="n">
-        <v>6515240</v>
+        <v>6515245</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Finspång</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Skedevi</t>
+          <t>Simonstorp</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121500789</v>
+        <v>121500341</v>
       </c>
       <c r="B5" t="n">
-        <v>79724</v>
+        <v>79690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562707</v>
+        <v>562649</v>
       </c>
       <c r="R5" t="n">
-        <v>6515242</v>
+        <v>6515253</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500341</v>
+        <v>121500825</v>
       </c>
       <c r="B6" t="n">
-        <v>79689</v>
+        <v>88506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1099,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>805</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Scharlakansvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562649</v>
+        <v>562686</v>
       </c>
       <c r="R6" t="n">
-        <v>6515253</v>
+        <v>6515292</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1177,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500825</v>
+        <v>121500789</v>
       </c>
       <c r="B7" t="n">
-        <v>88505</v>
+        <v>79725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,45 +1201,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>805</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562686</v>
+        <v>562707</v>
       </c>
       <c r="R7" t="n">
-        <v>6515292</v>
+        <v>6515242</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 51531-2024 artfynd.xlsx
+++ b/artfynd/A 51531-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121500809</v>
+        <v>121500825</v>
       </c>
       <c r="B4" t="n">
-        <v>94595</v>
+        <v>88506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>805</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Scharlakansvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562703</v>
+        <v>562686</v>
       </c>
       <c r="R4" t="n">
-        <v>6515245</v>
+        <v>6515292</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +973,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121500341</v>
+        <v>121500789</v>
       </c>
       <c r="B5" t="n">
-        <v>79690</v>
+        <v>79725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +997,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562649</v>
+        <v>562707</v>
       </c>
       <c r="R5" t="n">
-        <v>6515253</v>
+        <v>6515242</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500825</v>
+        <v>121500809</v>
       </c>
       <c r="B6" t="n">
-        <v>88506</v>
+        <v>94595</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,45 +1099,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>805</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562686</v>
+        <v>562703</v>
       </c>
       <c r="R6" t="n">
-        <v>6515292</v>
+        <v>6515245</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,22 +1177,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500789</v>
+        <v>121500341</v>
       </c>
       <c r="B7" t="n">
-        <v>79725</v>
+        <v>79690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562707</v>
+        <v>562649</v>
       </c>
       <c r="R7" t="n">
-        <v>6515242</v>
+        <v>6515253</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>

--- a/artfynd/A 51531-2024 artfynd.xlsx
+++ b/artfynd/A 51531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121501806</v>
+        <v>121500341</v>
       </c>
       <c r="B2" t="n">
-        <v>79594</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562590</v>
+        <v>562649</v>
       </c>
       <c r="R2" t="n">
-        <v>6515240</v>
+        <v>6515253</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Finspång</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Skedevi</t>
+          <t>Simonstorp</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121500360</v>
+        <v>121500825</v>
       </c>
       <c r="B3" t="n">
-        <v>100371</v>
+        <v>88506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>805</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Scharlakansvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562643</v>
+        <v>562686</v>
       </c>
       <c r="R3" t="n">
-        <v>6515265</v>
+        <v>6515292</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +871,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121500825</v>
+        <v>121500809</v>
       </c>
       <c r="B4" t="n">
-        <v>88506</v>
+        <v>94595</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,45 +895,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>805</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562686</v>
+        <v>562703</v>
       </c>
       <c r="R4" t="n">
-        <v>6515292</v>
+        <v>6515245</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,22 +973,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121500789</v>
+        <v>121500360</v>
       </c>
       <c r="B5" t="n">
-        <v>79725</v>
+        <v>100371</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562707</v>
+        <v>562643</v>
       </c>
       <c r="R5" t="n">
-        <v>6515242</v>
+        <v>6515265</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500809</v>
+        <v>121501806</v>
       </c>
       <c r="B6" t="n">
-        <v>94595</v>
+        <v>79594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,37 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562703</v>
+        <v>562590</v>
       </c>
       <c r="R6" t="n">
-        <v>6515245</v>
+        <v>6515240</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Finspång</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Skedevi</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1177,22 +1177,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500341</v>
+        <v>121500789</v>
       </c>
       <c r="B7" t="n">
-        <v>79690</v>
+        <v>79725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562649</v>
+        <v>562707</v>
       </c>
       <c r="R7" t="n">
-        <v>6515253</v>
+        <v>6515242</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>

--- a/artfynd/A 51531-2024 artfynd.xlsx
+++ b/artfynd/A 51531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121500341</v>
+        <v>121500360</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>100371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562649</v>
+        <v>562643</v>
       </c>
       <c r="R2" t="n">
-        <v>6515253</v>
+        <v>6515265</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121500825</v>
+        <v>121500341</v>
       </c>
       <c r="B3" t="n">
-        <v>88506</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,41 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>805</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562686</v>
+        <v>562649</v>
       </c>
       <c r="R3" t="n">
-        <v>6515292</v>
+        <v>6515253</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121500809</v>
+        <v>121500789</v>
       </c>
       <c r="B4" t="n">
-        <v>94595</v>
+        <v>79725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562703</v>
+        <v>562707</v>
       </c>
       <c r="R4" t="n">
-        <v>6515245</v>
+        <v>6515242</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121500360</v>
+        <v>121501806</v>
       </c>
       <c r="B5" t="n">
-        <v>100371</v>
+        <v>79594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562643</v>
+        <v>562590</v>
       </c>
       <c r="R5" t="n">
-        <v>6515265</v>
+        <v>6515240</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1040,7 +1036,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Finspång</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1050,7 +1046,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Skedevi</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1075,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121501806</v>
+        <v>121500825</v>
       </c>
       <c r="B6" t="n">
-        <v>79594</v>
+        <v>88506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,41 +1095,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>805</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Scharlakansvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövkullen, Ög</t>
+          <t>Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562590</v>
+        <v>562686</v>
       </c>
       <c r="R6" t="n">
-        <v>6515240</v>
+        <v>6515292</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Finspång</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Skedevi</t>
+          <t>Simonstorp</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500789</v>
+        <v>121500809</v>
       </c>
       <c r="B7" t="n">
-        <v>79725</v>
+        <v>94595</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562707</v>
+        <v>562703</v>
       </c>
       <c r="R7" t="n">
-        <v>6515242</v>
+        <v>6515245</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 51531-2024 artfynd.xlsx
+++ b/artfynd/A 51531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121500360</v>
+        <v>121501806</v>
       </c>
       <c r="B2" t="n">
-        <v>100371</v>
+        <v>79601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562643</v>
+        <v>562590</v>
       </c>
       <c r="R2" t="n">
-        <v>6515265</v>
+        <v>6515240</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Finspång</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Skedevi</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121500341</v>
+        <v>121500360</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>100379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562649</v>
+        <v>562643</v>
       </c>
       <c r="R3" t="n">
-        <v>6515253</v>
+        <v>6515265</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -882,7 +882,7 @@
         <v>121500789</v>
       </c>
       <c r="B4" t="n">
-        <v>79725</v>
+        <v>79732</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501806</v>
+        <v>121500825</v>
       </c>
       <c r="B5" t="n">
-        <v>79594</v>
+        <v>88513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>805</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Scharlakansvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövkullen, Ög</t>
+          <t>Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562590</v>
+        <v>562686</v>
       </c>
       <c r="R5" t="n">
-        <v>6515240</v>
+        <v>6515292</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Finspång</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1046,7 +1050,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Skedevi</t>
+          <t>Simonstorp</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500825</v>
+        <v>121500341</v>
       </c>
       <c r="B6" t="n">
-        <v>88506</v>
+        <v>79697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,41 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>805</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562686</v>
+        <v>562649</v>
       </c>
       <c r="R6" t="n">
-        <v>6515292</v>
+        <v>6515253</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,12 +1177,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1192,7 +1192,7 @@
         <v>121500809</v>
       </c>
       <c r="B7" t="n">
-        <v>94595</v>
+        <v>94603</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 51531-2024 artfynd.xlsx
+++ b/artfynd/A 51531-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121500341</v>
+        <v>121500809</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>94603</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562649</v>
+        <v>562703</v>
       </c>
       <c r="R3" t="n">
-        <v>6515253</v>
+        <v>6515245</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500809</v>
+        <v>121500789</v>
       </c>
       <c r="B6" t="n">
-        <v>94603</v>
+        <v>79732</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562703</v>
+        <v>562707</v>
       </c>
       <c r="R6" t="n">
-        <v>6515245</v>
+        <v>6515242</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500789</v>
+        <v>121500341</v>
       </c>
       <c r="B7" t="n">
-        <v>79732</v>
+        <v>79697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562707</v>
+        <v>562649</v>
       </c>
       <c r="R7" t="n">
-        <v>6515242</v>
+        <v>6515253</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>

--- a/artfynd/A 51531-2024 artfynd.xlsx
+++ b/artfynd/A 51531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121500825</v>
+        <v>121500809</v>
       </c>
       <c r="B2" t="n">
-        <v>88513</v>
+        <v>94603</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>805</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenkullen, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562686</v>
+        <v>562703</v>
       </c>
       <c r="R2" t="n">
-        <v>6515292</v>
+        <v>6515245</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121500809</v>
+        <v>121500825</v>
       </c>
       <c r="B3" t="n">
-        <v>94603</v>
+        <v>88513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,41 +789,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>805</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Scharlakansvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562703</v>
+        <v>562686</v>
       </c>
       <c r="R3" t="n">
-        <v>6515245</v>
+        <v>6515292</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,12 +871,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500789</v>
+        <v>121500341</v>
       </c>
       <c r="B6" t="n">
-        <v>79732</v>
+        <v>79697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,25 +1099,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562707</v>
+        <v>562649</v>
       </c>
       <c r="R6" t="n">
-        <v>6515242</v>
+        <v>6515253</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500341</v>
+        <v>121500789</v>
       </c>
       <c r="B7" t="n">
-        <v>79697</v>
+        <v>79732</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562649</v>
+        <v>562707</v>
       </c>
       <c r="R7" t="n">
-        <v>6515253</v>
+        <v>6515242</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>

--- a/artfynd/A 51531-2024 artfynd.xlsx
+++ b/artfynd/A 51531-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121500341</v>
+        <v>121500825</v>
       </c>
       <c r="B2" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>805</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562649</v>
+        <v>562686</v>
       </c>
       <c r="R2" t="n">
-        <v>6515253</v>
+        <v>6515292</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,69 +764,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121500825</v>
+        <v>121500718</v>
       </c>
       <c r="B3" t="n">
-        <v>88513</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>805</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkullen, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562686</v>
+        <v>562703</v>
       </c>
       <c r="R3" t="n">
-        <v>6515292</v>
+        <v>6515300</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,27 +861,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121501806</v>
+        <v>121500378</v>
       </c>
       <c r="B4" t="n">
-        <v>79601</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,37 +884,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövkullen, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562590</v>
+        <v>562653</v>
       </c>
       <c r="R4" t="n">
-        <v>6515240</v>
+        <v>6515311</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -938,7 +923,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Finspång</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -948,7 +933,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Skedevi</t>
+          <t>Simonstorp</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -973,27 +958,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121500789</v>
+        <v>121500476</v>
       </c>
       <c r="B5" t="n">
-        <v>79732</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Stenkullen, Stenkullen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562707</v>
+        <v>562698</v>
       </c>
       <c r="R5" t="n">
-        <v>6515242</v>
+        <v>6515318</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1087,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500360</v>
+        <v>121500809</v>
       </c>
       <c r="B6" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,13 +1102,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562643</v>
+        <v>562703</v>
       </c>
       <c r="R6" t="n">
-        <v>6515265</v>
+        <v>6515245</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,15 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500809</v>
+        <v>121501806</v>
       </c>
       <c r="B7" t="n">
-        <v>94603</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,37 +1175,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lövkullen, Lövkullen, Ög</t>
+          <t>Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562703</v>
+        <v>562590</v>
       </c>
       <c r="R7" t="n">
-        <v>6515245</v>
+        <v>6515240</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1244,7 +1214,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Finspång</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1254,7 +1224,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Skedevi</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1279,15 +1249,1197 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121500168</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lövkullen, Lövkullen, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>562589</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6515228</v>
+      </c>
+      <c r="S8" t="n">
+        <v>17</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Eva Siljeholm</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm, Jonas Edlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121500213</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lövkullen, Lövkullen, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562640</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6515226</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
         <is>
           <t>Eva Siljeholm</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121500341</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lövkullen, Lövkullen, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562649</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6515253</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121501766</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lövkullen, Lövkullen, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>562608</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6515231</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122273724</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svallberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>562605</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6515230</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121500226</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lövkullen, Lövkullen, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>562640</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6515226</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121500789</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lövkullen, Lövkullen, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562707</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6515242</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>92005830</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>562653</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6515019</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-10-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-10-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Vesa Jussila</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>111054428</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lövkullen, Lövkullen, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>562673</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6515066</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jonas Edlund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jonas Edlund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121500360</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lövkullen, Lövkullen, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>562643</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6515265</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121500761</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lövkullen, Lövkullen, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>562721</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6515236</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122273729</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svallberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>562721</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6515233</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
